--- a/2° Semestre/BD/Aula02/bd_aula02/bd_mer_der_aula02/dicionario.xlsx
+++ b/2° Semestre/BD/Aula02/bd_aula02/bd_mer_der_aula02/dicionario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme Barichello\Desktop\bd_aula02\bd_mer_der_aula02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme Barichello\Desktop\SENAI\2° Semestre\BD\Aula02\bd_aula02\bd_mer_der_aula02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E6878B-648A-40B5-83F3-288C14EA2728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFA4940-918C-40D4-BFC9-5B584732F5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="3" xr2:uid="{4379698F-7957-4FEE-AAAD-9A658EF27713}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4379698F-7957-4FEE-AAAD-9A658EF27713}"/>
   </bookViews>
   <sheets>
     <sheet name="Consultas" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="99">
   <si>
     <t>id</t>
   </si>
@@ -273,13 +273,79 @@
   </si>
   <si>
     <t>Veterinario</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Chave primária</t>
+  </si>
+  <si>
+    <t>Chave estrangeira, referência: Consulta (id)</t>
+  </si>
+  <si>
+    <t>Chave estrangeira, referência: Veterinario (id)</t>
+  </si>
+  <si>
+    <t>O tipo de consulta</t>
+  </si>
+  <si>
+    <t>Descrição do tipo de consulta</t>
+  </si>
+  <si>
+    <t>Preço da consulta correspondente</t>
+  </si>
+  <si>
+    <t>Preço alterado caso animal seja de porte grande</t>
+  </si>
+  <si>
+    <t>Nome do cliente</t>
+  </si>
+  <si>
+    <t>Nome do veterinario</t>
+  </si>
+  <si>
+    <t>Porte do animal do cliente</t>
+  </si>
+  <si>
+    <t>Se o animal é doméstico ou silvestre</t>
+  </si>
+  <si>
+    <t>Qual animal é</t>
+  </si>
+  <si>
+    <t>Data de quando foi registrado o atendimento</t>
+  </si>
+  <si>
+    <t>Quanto foi pago pela consulta</t>
+  </si>
+  <si>
+    <t>Quanto foi pago pelo serviço do veterinario</t>
+  </si>
+  <si>
+    <t>Valor total somando o dois custos</t>
+  </si>
+  <si>
+    <t>Em que o veterinario é formado</t>
+  </si>
+  <si>
+    <t>Custo pelo serviço</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +362,23 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -323,13 +406,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1492,6 +1577,7 @@
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1507,7 +1593,7 @@
       <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1518,6 +1604,15 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1526,6 +1621,15 @@
       <c r="B3" t="s">
         <v>1</v>
       </c>
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1534,6 +1638,15 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1542,6 +1655,15 @@
       <c r="B5" t="s">
         <v>3</v>
       </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1550,6 +1672,15 @@
       <c r="B6" t="s">
         <v>70</v>
       </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1558,6 +1689,15 @@
       <c r="B7" t="s">
         <v>0</v>
       </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1566,6 +1706,15 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1574,6 +1723,15 @@
       <c r="B9" t="s">
         <v>72</v>
       </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1582,6 +1740,15 @@
       <c r="B10" t="s">
         <v>18</v>
       </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1590,6 +1757,15 @@
       <c r="B11" t="s">
         <v>19</v>
       </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11">
+        <v>40</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1598,6 +1774,15 @@
       <c r="B12" t="s">
         <v>1</v>
       </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1606,6 +1791,15 @@
       <c r="B13" t="s">
         <v>23</v>
       </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13">
+        <v>40</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1614,6 +1808,12 @@
       <c r="B14" t="s">
         <v>25</v>
       </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1622,6 +1822,15 @@
       <c r="B15" t="s">
         <v>62</v>
       </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1630,45 +1839,99 @@
       <c r="B16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
       <c r="B17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18">
+        <v>11</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19">
+        <v>40</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>76</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20">
+        <v>40</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>76</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/2° Semestre/BD/Aula02/bd_aula02/bd_mer_der_aula02/dicionario.xlsx
+++ b/2° Semestre/BD/Aula02/bd_aula02/bd_mer_der_aula02/dicionario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme Barichello\Desktop\SENAI\2° Semestre\BD\Aula02\bd_aula02\bd_mer_der_aula02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFA4940-918C-40D4-BFC9-5B584732F5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C62EEA-D61C-4872-A2C4-0B0E1B68ACEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4379698F-7957-4FEE-AAAD-9A658EF27713}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4379698F-7957-4FEE-AAAD-9A658EF27713}"/>
   </bookViews>
   <sheets>
     <sheet name="Consultas" sheetId="1" r:id="rId1"/>
@@ -92,9 +92,6 @@
     <t>Reavaliação para checar a melhora do animal em até 15 dias</t>
   </si>
   <si>
-    <t>grande porte +20%</t>
-  </si>
-  <si>
     <t>id_consulta</t>
   </si>
   <si>
@@ -339,6 +336,9 @@
   </si>
   <si>
     <t>Custo pelo serviço</t>
+  </si>
+  <si>
+    <t>grande_porte</t>
   </si>
 </sst>
 </file>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -906,34 +906,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>63</v>
-      </c>
-      <c r="K1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -947,16 +947,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1">
         <v>45940</v>
@@ -983,16 +983,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1">
         <v>45940</v>
@@ -1019,16 +1019,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
       </c>
       <c r="H4" s="1">
         <v>45941</v>
@@ -1055,16 +1055,16 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
         <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
       </c>
       <c r="H5" s="1">
         <v>45941</v>
@@ -1091,16 +1091,16 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
         <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="1">
         <v>45941</v>
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
       </c>
       <c r="H7" s="1">
         <v>45941</v>
@@ -1163,16 +1163,16 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
         <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="1">
         <v>45942</v>
@@ -1199,16 +1199,16 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
       </c>
       <c r="H9" s="1">
         <v>45942</v>
@@ -1235,16 +1235,16 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
         <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
       </c>
       <c r="H10" s="1">
         <v>45942</v>
@@ -1271,16 +1271,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
         <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>46</v>
       </c>
       <c r="H11" s="1">
         <v>45942</v>
@@ -1307,16 +1307,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>21</v>
       </c>
-      <c r="F13" t="s">
-        <v>22</v>
-      </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="1">
         <v>45946</v>
@@ -1343,16 +1343,16 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H14" s="1">
         <v>45947</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1405,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>120</v>
@@ -1419,7 +1419,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3">
         <v>115</v>
@@ -1430,10 +1430,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>300</v>
@@ -1444,10 +1444,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>320</v>
@@ -1458,10 +1458,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>295</v>
@@ -1475,7 +1475,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>500</v>
@@ -1489,7 +1489,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>480</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9">
         <v>490</v>
@@ -1517,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>200</v>
@@ -1531,7 +1531,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11">
         <v>200</v>
@@ -1545,7 +1545,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12">
         <v>350</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13">
         <v>325</v>
@@ -1582,356 +1582,356 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3">
         <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4">
         <v>200</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5">
         <v>10.199999999999999</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>10.199999999999999</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7">
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8">
         <v>11</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9">
         <v>11</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10">
         <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11">
         <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D13">
         <v>40</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15">
         <v>10.199999999999999</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16">
         <v>10.199999999999999</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17">
         <v>10.199999999999999</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18">
         <v>11</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19">
         <v>40</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21">
         <v>10.199999999999999</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/2° Semestre/BD/Aula02/bd_aula02/bd_mer_der_aula02/dicionario.xlsx
+++ b/2° Semestre/BD/Aula02/bd_aula02/bd_mer_der_aula02/dicionario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme Barichello\Desktop\SENAI\2° Semestre\BD\Aula02\bd_aula02\bd_mer_der_aula02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C62EEA-D61C-4872-A2C4-0B0E1B68ACEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1CADC9-22EC-4EA9-8340-D7905DEE3CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4379698F-7957-4FEE-AAAD-9A658EF27713}"/>
   </bookViews>
@@ -62,12 +62,6 @@
     <t>Especialistas</t>
   </si>
   <si>
-    <t>Dermatologia, Cardiologia, Oncologia, Ortopedia, Oftalmologia, Endocrinologia, etc.</t>
-  </si>
-  <si>
-    <t>Check-ups, aplicação de vacinas, receitas comuns e orientações gerais em horário comercial</t>
-  </si>
-  <si>
     <t>Atendimentos fora do horário comercial</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t>Animais Silvestres</t>
   </si>
   <si>
-    <t>Atendimento especializado para aves, roedores, répteis e coelhos</t>
-  </si>
-  <si>
     <t>Retorno Veterinário</t>
   </si>
   <si>
@@ -339,6 +330,15 @@
   </si>
   <si>
     <t>grande_porte</t>
+  </si>
+  <si>
+    <t>Dermatologia; Cardiologia; Oncologia; Ortopedia; Oftalmologia; Endocrinologia; etc.</t>
+  </si>
+  <si>
+    <t>Check-ups; aplicação de vacinas; receitas comuns e orientações gerais em horário comercial</t>
+  </si>
+  <si>
+    <t>Atendimento especializado para aves; roedores; répteis; coelhos</t>
   </si>
 </sst>
 </file>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="D2">
         <v>120</v>
@@ -800,7 +800,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D3">
         <v>300</v>
@@ -815,10 +815,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>500</v>
@@ -833,10 +833,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5">
         <v>200</v>
@@ -851,10 +851,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="D6">
         <v>350</v>
@@ -869,10 +869,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -906,34 +906,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -947,16 +947,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1">
         <v>45940</v>
@@ -983,16 +983,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1">
         <v>45940</v>
@@ -1019,16 +1019,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
       </c>
       <c r="H4" s="1">
         <v>45941</v>
@@ -1055,16 +1055,16 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1">
         <v>45941</v>
@@ -1091,16 +1091,16 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
       </c>
       <c r="H6" s="1">
         <v>45941</v>
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1">
         <v>45941</v>
@@ -1163,16 +1163,16 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H8" s="1">
         <v>45942</v>
@@ -1199,16 +1199,16 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H9" s="1">
         <v>45942</v>
@@ -1235,16 +1235,16 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H10" s="1">
         <v>45942</v>
@@ -1271,16 +1271,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1">
         <v>45942</v>
@@ -1307,16 +1307,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H13" s="1">
         <v>45946</v>
@@ -1343,16 +1343,16 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H14" s="1">
         <v>45947</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1405,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>120</v>
@@ -1419,7 +1419,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>115</v>
@@ -1430,10 +1430,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D4">
         <v>300</v>
@@ -1444,10 +1444,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>320</v>
@@ -1458,10 +1458,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>295</v>
@@ -1472,10 +1472,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>500</v>
@@ -1486,10 +1486,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>480</v>
@@ -1500,10 +1500,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>490</v>
@@ -1514,10 +1514,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>200</v>
@@ -1528,10 +1528,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11">
         <v>200</v>
@@ -1542,10 +1542,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>350</v>
@@ -1556,10 +1556,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D13">
         <v>325</v>
@@ -1582,356 +1582,356 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3">
         <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4">
         <v>200</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D5">
         <v>10.199999999999999</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D6">
         <v>10.199999999999999</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>73</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
       </c>
       <c r="D8">
         <v>11</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
       </c>
       <c r="D9">
         <v>11</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10">
         <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D11">
         <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13">
         <v>40</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D15">
         <v>10.199999999999999</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16">
         <v>10.199999999999999</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17">
         <v>10.199999999999999</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D18">
         <v>11</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D19">
         <v>40</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
         <v>75</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
       </c>
       <c r="D21">
         <v>10.199999999999999</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
